--- a/data/trans_orig/IQ2605_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ2605_R2-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>43809</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>36875</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>51071</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>51,99%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>43,76%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>60,61%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>44097</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>37317</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>52238</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>36802</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>51666</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>49,59%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>41,96%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>58,74%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>43809</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>36630</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>50729</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>51,99%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>77558</t>
+          <t>76488</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>98487</t>
+          <t>98131</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>56,66%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>40458</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>33196</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>47392</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>48,01%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>39,39%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>56,24%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>44828</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>36687</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>51608</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>37259</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>52123</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>50,41%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>41,26%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>58,04%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>40458</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>33538</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>47637</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>48,01%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>58,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>74705</t>
+          <t>75061</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>95634</t>
+          <t>96704</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>55,84%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>84267</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>84267</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>84267</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>88925</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>88925</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>88925</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>84267</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>84267</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>84267</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>238745</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>222443</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>255726</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>51,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>47,52%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>54,63%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>334</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>220328</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>204333</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>237537</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>203906</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>237910</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>54,21%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>50,28%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>58,45%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>359</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>238745</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>222260</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>258140</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>51,0%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>437612</t>
+          <t>435732</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>484118</t>
+          <t>483506</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>55,29%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>229363</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>212382</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>245665</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>49,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>45,37%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>52,48%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>279</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>186086</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>168877</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>202081</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>168504</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>202508</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>45,79%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>41,55%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>49,72%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>347</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>229363</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>209968</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>245848</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>49,0%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>390404</t>
+          <t>391016</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>436910</t>
+          <t>438790</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>50,17%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>706</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>468108</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>468108</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>468108</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>613</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>406414</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>406414</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>406414</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>706</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>468108</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>468108</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>468108</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>90121</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>79916</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>99606</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>58,7%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>52,05%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>64,88%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>137</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>94154</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>83372</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>104400</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>84252</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>105064</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>55,61%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>49,24%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>61,66%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>90121</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>80405</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>100517</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>58,7%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>169920</t>
+          <t>170284</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>199391</t>
+          <t>198300</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,42%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>63403</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>53918</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>73608</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>41,3%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>35,12%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>47,95%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>75169</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>64923</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>85951</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>64259</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>85071</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>44,39%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>38,34%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>50,76%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>63403</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>53007</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>73119</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>41,3%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>123456</t>
+          <t>124547</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>152927</t>
+          <t>152563</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>47,26%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>153524</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>153524</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>153524</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>169323</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>169323</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>169323</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>153524</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>153524</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>153524</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>372675</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>349455</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>392941</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>52,79%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>49,51%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>55,67%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>538</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>358579</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>336981</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>378576</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>339361</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>379085</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>53,95%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>50,7%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>56,96%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>559</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>372675</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>351075</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>391885</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>52,79%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>698754</t>
+          <t>699407</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>760010</t>
+          <t>757448</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>55,27%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>502</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>333224</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>312958</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>356444</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>47,21%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>44,33%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>50,49%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>454</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>306084</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>286087</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>327682</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>285578</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>325302</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>46,05%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>43,04%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>49,3%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>502</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>333224</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>314014</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>354824</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>47,21%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>610552</t>
+          <t>613114</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>671808</t>
+          <t>671155</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>48,97%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1061</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>705899</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>705899</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>705899</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>992</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>664663</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>664663</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>664663</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1061</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>705899</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>705899</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>705899</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>62380</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>55048</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>68473</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>73,49%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>64,85%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>80,67%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>65210</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>57364</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>71271</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>57910</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>71581</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>72,36%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>63,65%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>79,08%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>62380</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>54362</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>68555</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>73,49%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>117305</t>
+          <t>117833</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>136342</t>
+          <t>136578</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>78,04%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>22504</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>16411</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>29836</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>26,51%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>19,33%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>35,15%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>24910</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>18849</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>32756</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>18539</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>32210</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>27,64%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>20,92%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>36,35%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>22504</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>16329</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>30522</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>26,51%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38661</t>
+          <t>38425</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57698</t>
+          <t>57170</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,67%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>84884</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>84884</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>84884</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>131</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90120</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90120</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90120</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>84884</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>84884</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>84884</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>506</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>351404</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>335432</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>367144</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>73,85%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>70,5%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>77,16%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>467</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>321169</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>305266</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>335147</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>305916</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>335916</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>73,27%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>69,64%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>76,46%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>506</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>351404</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>336105</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>368424</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>73,85%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>649845</t>
+          <t>647831</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>693815</t>
+          <t>693217</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>75,83%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>124406</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>108666</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>140378</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>26,15%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>22,84%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>29,5%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>117160</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>103182</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>133063</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>102413</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>132413</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>26,73%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>23,54%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>30,36%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>124406</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>107386</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>139705</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>26,15%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>220324</t>
+          <t>220922</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>264294</t>
+          <t>266308</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,13%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>682</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>475810</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>475810</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>475810</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>633</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>438329</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>438329</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>438329</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>682</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>475810</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>475810</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>475810</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>116334</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>106431</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>126431</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>71,18%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>65,12%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>77,36%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>170</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>119926</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>110130</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>128644</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>110461</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>128535</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>75,23%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>69,08%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>80,69%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>116334</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>106097</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>125021</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>71,18%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>222025</t>
+          <t>220882</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>247814</t>
+          <t>247790</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>76,75%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>47102</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>37005</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>57005</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>28,82%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>22,64%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>34,88%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>39494</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>30776</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>49290</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>30885</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>48959</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>24,77%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>19,31%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>30,92%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>47102</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>38415</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>57339</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>28,82%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>75042</t>
+          <t>75066</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>100831</t>
+          <t>101974</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,59%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>163436</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>163436</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>163436</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>159420</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>159420</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>159420</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>163436</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>163436</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>163436</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>757</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>530118</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>510185</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>550137</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>73,21%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>70,45%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>75,97%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>733</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>506305</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>486435</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>527029</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>485730</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>525483</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>73,6%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>70,72%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>76,62%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>757</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>530118</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>510291</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>549655</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>73,21%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1009213</t>
+          <t>1007544</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1063594</t>
+          <t>1063101</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>75,29%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>194012</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>173993</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>213945</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>26,79%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>24,03%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>29,55%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>181563</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>160839</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>201433</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>162385</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>202138</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>26,4%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>23,38%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>29,28%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>194012</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>174475</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>213839</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>26,79%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>348404</t>
+          <t>348897</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>402785</t>
+          <t>404454</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,64%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1032</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>724130</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>724130</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>724130</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>990</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>687868</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>687868</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>687868</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1032</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>724130</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>724130</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>724130</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>56409</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>49408</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>60791</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>82,21%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>72,01%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>88,6%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>46681</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>41358</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>51259</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>40894</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>51054</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>79,38%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>70,33%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>87,16%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>56409</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>50018</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>60702</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>82,21%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>94160</t>
+          <t>94996</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>110350</t>
+          <t>109822</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,19%</t>
         </is>
       </c>
     </row>
@@ -4047,67 +4047,67 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>12205</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7823</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>19206</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>17,79%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>11,4%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>27,99%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>12127</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>7549</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>17450</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>7754</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>17914</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>20,62%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>12,84%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>29,67%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>12205</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>7912</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>18596</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>17,79%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17072</t>
+          <t>17600</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33262</t>
+          <t>32426</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>25,45%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>58808</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>58808</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>58808</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>542</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>380157</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>364740</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>393743</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>78,14%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>74,97%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>80,93%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>536</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>350911</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>334275</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>363637</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>334410</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>365440</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>75,48%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>71,9%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>78,22%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>542</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>380157</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>365213</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>394309</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>78,14%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>708673</t>
+          <t>707017</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>754078</t>
+          <t>753811</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,23%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>106337</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>92751</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>121754</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>21,86%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>19,07%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>25,03%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>114004</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>101278</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>130640</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>99475</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>130505</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>24,52%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>21,78%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>28,1%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>106337</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>92185</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>121281</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>21,86%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>197331</t>
+          <t>197598</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>242736</t>
+          <t>244392</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,69%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>486494</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>486494</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>486494</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>702</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>464915</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>464915</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>464915</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>692</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>486494</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>486494</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>486494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>147208</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>138151</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>154782</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>80,78%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>75,81%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>84,94%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>128499</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>118210</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>137230</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>117788</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>136723</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>76,32%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>70,21%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>81,51%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>147208</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>138343</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>156012</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>80,78%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>69,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>262503</t>
+          <t>260596</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>287509</t>
+          <t>288145</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,19%</t>
         </is>
       </c>
     </row>
@@ -4728,72 +4728,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>35015</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>27441</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>44072</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>19,22%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>15,06%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>24,19%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>39868</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>31137</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>50157</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>31644</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>50579</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>23,68%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>18,49%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>29,79%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>35015</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>26211</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>43880</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>19,22%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>63081</t>
+          <t>62445</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>88087</t>
+          <t>89994</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,67%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>182223</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>182223</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>182223</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>251</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>168367</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>168367</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>168367</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>182223</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>182223</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>182223</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>837</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>583776</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>563535</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>600903</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>79,17%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>76,43%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>81,5%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>800</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>526091</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>507772</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>543676</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>507027</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>543833</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>76,01%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>73,37%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>78,56%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>837</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>583776</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>562734</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>600860</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>79,17%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1082965</t>
+          <t>1082220</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1135614</t>
+          <t>1134290</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,35%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>153556</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>136429</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>173797</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>20,83%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>18,5%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>23,57%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>165998</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>148413</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>184317</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>148256</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>185062</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>23,99%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>21,44%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>26,63%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>153556</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>136472</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>174598</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>20,83%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>293807</t>
+          <t>295131</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>346456</t>
+          <t>347201</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,29%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1054</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>737332</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>737332</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>737332</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1041</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>692089</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>692089</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>692089</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1054</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>737332</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>737332</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>737332</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7373</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11831</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>83,95%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>59,49%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>95,47%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>8782</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5939</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10848</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>78,02%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>52,77%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>96,37%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11039</t>
+          <t>5958</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7707</t>
+          <t>3600</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12833</t>
+          <t>7574</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>19821</t>
+          <t>16362</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15945</t>
+          <t>13275</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22849</t>
+          <t>18711</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>90,42%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>562</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5020</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2790</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>727</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6122</t>
+          <t>4701</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>4332</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2236</t>
+          <t>1983</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9140</t>
+          <t>7419</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>35,85%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12393</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12393</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12393</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>11256</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>11256</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>11256</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13829</t>
+          <t>8301</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13829</t>
+          <t>8301</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13829</t>
+          <t>8301</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>25085</t>
+          <t>20694</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>25085</t>
+          <t>20694</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>25085</t>
+          <t>20694</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>94009</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>85145</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>101827</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>76,5%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>69,29%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>82,86%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>61685</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>54325</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>68998</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>69,63%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>61,32%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>77,89%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>102590</t>
+          <t>60621</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>92945</t>
+          <t>53102</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>110673</t>
+          <t>67808</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>164277</t>
+          <t>154630</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>151854</t>
+          <t>143433</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>175831</t>
+          <t>164557</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>78,19%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>28879</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>21061</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>37743</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>23,5%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>17,14%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>30,71%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>26904</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>19591</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>34264</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>30,37%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>22,11%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>38,68%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>30629</t>
+          <t>26958</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>22546</t>
+          <t>19771</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>40274</t>
+          <t>34477</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>57532</t>
+          <t>55837</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>45978</t>
+          <t>45910</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>69955</t>
+          <t>67034</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,85%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>122888</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>122888</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>122888</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>88589</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>88589</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>88589</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>133219</t>
+          <t>87579</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>133219</t>
+          <t>87579</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>133219</t>
+          <t>87579</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>221809</t>
+          <t>210467</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>221809</t>
+          <t>210467</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>221809</t>
+          <t>210467</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,44 +6218,44 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>31754</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>25410</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>36442</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>73,7%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>58,98%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>84,58%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>32437</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>27088</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>36353</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>75,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>62,63%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>84,06%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
           <t>32818</t>
@@ -6263,27 +6263,27 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27569</t>
+          <t>27256</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38112</t>
+          <t>36870</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>65256</t>
+          <t>64571</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57680</t>
+          <t>56618</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71809</t>
+          <t>70759</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,58%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>11330</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6642</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>17674</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>26,3%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>15,42%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>41,02%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>10811</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>6895</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>16160</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>25,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>15,94%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>37,37%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11903</t>
+          <t>10837</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6609</t>
+          <t>6785</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17152</t>
+          <t>16399</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>22714</t>
+          <t>22167</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16161</t>
+          <t>15979</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30290</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,73%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>43084</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>43084</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>43084</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>43248</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>43248</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>43248</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>44721</t>
+          <t>43655</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>44721</t>
+          <t>43655</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>44721</t>
+          <t>43655</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>87970</t>
+          <t>86738</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>87970</t>
+          <t>86738</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>87970</t>
+          <t>86738</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>136167</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>126085</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>145254</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>76,34%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>70,69%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>81,44%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>102905</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>93844</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>111272</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>71,91%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>65,58%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>77,76%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>146448</t>
+          <t>99396</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>134765</t>
+          <t>89886</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>157301</t>
+          <t>107975</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>249353</t>
+          <t>235563</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>236071</t>
+          <t>221415</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>263118</t>
+          <t>248795</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,26%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>42198</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>33111</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>52280</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>23,66%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>18,56%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>29,31%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>40188</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>31821</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>49249</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>28,09%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>22,24%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>34,42%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>45322</t>
+          <t>40138</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>34469</t>
+          <t>31559</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>57005</t>
+          <t>49648</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>85510</t>
+          <t>82336</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>71745</t>
+          <t>69104</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>98792</t>
+          <t>96484</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>30,35%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>178365</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>178365</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>178365</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>224</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>143093</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>143093</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>143093</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>191770</t>
+          <t>139534</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>191770</t>
+          <t>139534</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>191770</t>
+          <t>139534</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>334863</t>
+          <t>317899</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>334863</t>
+          <t>317899</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>334863</t>
+          <t>317899</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
